--- a/ПримерРасчета.xlsx
+++ b/ПримерРасчета.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\LehaLab\lab1_2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8472DB8-78A4-4269-9B35-C62C4E20A959}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA912C62-9146-483C-82DD-866C7156F46C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-17400" windowWidth="30960" windowHeight="16800" xr2:uid="{43840C9A-576F-488B-B11D-21A699DC727D}"/>
   </bookViews>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -538,7 +538,7 @@
         <v>1</v>
       </c>
       <c r="C1">
-        <v>50</v>
+        <v>120.5</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
@@ -549,7 +549,7 @@
         <v>2</v>
       </c>
       <c r="C2">
-        <v>60</v>
+        <v>95</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -560,7 +560,7 @@
         <v>3</v>
       </c>
       <c r="C3">
-        <v>18.399999999999999</v>
+        <v>64</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -571,7 +571,7 @@
         <v>8</v>
       </c>
       <c r="C4">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -582,7 +582,7 @@
         <v>10</v>
       </c>
       <c r="C5">
-        <v>30</v>
+        <v>54.5</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -593,7 +593,7 @@
         <v>12</v>
       </c>
       <c r="C6">
-        <v>0.48</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -604,7 +604,7 @@
         <v>13</v>
       </c>
       <c r="C7">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -616,7 +616,7 @@
       </c>
       <c r="C9">
         <f>duration_minutes/60</f>
-        <v>1</v>
+        <v>1.5833333333333333</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -628,7 +628,7 @@
       </c>
       <c r="C10" cm="1">
         <f t="array" ref="C10">battery_capacity_kwh*(start_charge_percent-finish_charge_percent)/100</f>
-        <v>9.1999999999999993</v>
+        <v>17.600000000000001</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
@@ -640,7 +640,7 @@
       </c>
       <c r="C11">
         <f>distance_km/time_hours</f>
-        <v>50</v>
+        <v>76.10526315789474</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
@@ -652,7 +652,7 @@
       </c>
       <c r="C12" cm="1">
         <f t="array" ref="C12">energy_used_kwh/distance_km*100</f>
-        <v>18.399999999999999</v>
+        <v>14.605809128630707</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
@@ -664,7 +664,7 @@
       </c>
       <c r="C13" cm="1">
         <f t="array" ref="C13">energy_used_kwh*tariff_byn_per_kwh</f>
-        <v>4.4159999999999995</v>
+        <v>7.3920000000000003</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
@@ -676,7 +676,7 @@
       </c>
       <c r="C14" cm="1">
         <f t="array" ref="C14">trip_cost_byn/passengers</f>
-        <v>2.2079999999999997</v>
+        <v>2.464</v>
       </c>
     </row>
   </sheetData>
